--- a/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
@@ -16856,7 +16856,7 @@
         <v>8030</v>
       </c>
       <c r="S16" s="306" t="n">
-        <v>9525.098</v>
+        <v>9522.797999999999</v>
       </c>
       <c r="T16" s="308">
         <f>S16-R16</f>
@@ -17124,7 +17124,7 @@
         <v>120</v>
       </c>
       <c r="S19" s="355" t="n">
-        <v>299.935</v>
+        <v>297.615</v>
       </c>
       <c r="T19" s="317">
         <f>S19-R19</f>
@@ -18086,7 +18086,7 @@
         <v>9410</v>
       </c>
       <c r="S30" s="368" t="n">
-        <v>8386.043999999998</v>
+        <v>8385.643999999998</v>
       </c>
       <c r="T30" s="308">
         <f>S30-R30</f>
@@ -21049,7 +21049,7 @@
         <v>31450</v>
       </c>
       <c r="L16" s="306" t="n">
-        <v>39461.68</v>
+        <v>39502.261</v>
       </c>
       <c r="M16" s="308">
         <f>L16-K16</f>
@@ -21073,7 +21073,7 @@
         <v>7770</v>
       </c>
       <c r="S16" s="306" t="n">
-        <v>10096.258</v>
+        <v>10136.7791</v>
       </c>
       <c r="T16" s="308">
         <f>S16-R16</f>
@@ -21509,7 +21509,7 @@
         <v>7020</v>
       </c>
       <c r="S21" s="357" t="n">
-        <v>9481.314</v>
+        <v>9373.103999999999</v>
       </c>
       <c r="T21" s="308">
         <f>S21-R21</f>
@@ -22547,7 +22547,7 @@
         <v>8100</v>
       </c>
       <c r="L33" s="355" t="n">
-        <v>3988.655</v>
+        <v>3995.015</v>
       </c>
       <c r="M33" s="317">
         <f>L33-K33</f>
@@ -22571,7 +22571,7 @@
         <v>1800</v>
       </c>
       <c r="S33" s="351" t="n">
-        <v>779.1</v>
+        <v>779.66</v>
       </c>
       <c r="T33" s="317">
         <f>S33-R33</f>
@@ -25290,7 +25290,7 @@
         <v>6710</v>
       </c>
       <c r="S16" s="306" t="n">
-        <v>7800.534</v>
+        <v>7856.482</v>
       </c>
       <c r="T16" s="308">
         <f>S16-R16</f>
@@ -26764,7 +26764,7 @@
         <v>27100</v>
       </c>
       <c r="L33" s="355" t="n">
-        <v>22289.31</v>
+        <v>24122.96</v>
       </c>
       <c r="M33" s="317">
         <f>L33-K33</f>
@@ -26788,7 +26788,7 @@
         <v>7210</v>
       </c>
       <c r="S33" s="351" t="n">
-        <v>6004.501</v>
+        <v>6541.401</v>
       </c>
       <c r="T33" s="317">
         <f>S33-R33</f>
@@ -28533,7 +28533,7 @@
         <v>68980</v>
       </c>
       <c r="L5" s="306" t="n">
-        <v>67381.86199999999</v>
+        <v>67381.91500000001</v>
       </c>
       <c r="M5" s="308">
         <f>L5-K5</f>
@@ -28557,7 +28557,7 @@
         <v>18460</v>
       </c>
       <c r="S5" s="310" t="n">
-        <v>20280.868</v>
+        <v>20280.897</v>
       </c>
       <c r="T5" s="308">
         <f>S5-R5</f>
@@ -29483,7 +29483,7 @@
         <v>26670</v>
       </c>
       <c r="L16" s="306" t="n">
-        <v>29622.077</v>
+        <v>29621.749</v>
       </c>
       <c r="M16" s="308">
         <f>L16-K16</f>
@@ -29507,7 +29507,7 @@
         <v>7030</v>
       </c>
       <c r="S16" s="306" t="n">
-        <v>8216.221</v>
+        <v>8303.685000000001</v>
       </c>
       <c r="T16" s="308">
         <f>S16-R16</f>
@@ -30713,7 +30713,7 @@
         <v>54050</v>
       </c>
       <c r="L30" s="306" t="n">
-        <v>54709.881</v>
+        <v>54710.01700000001</v>
       </c>
       <c r="M30" s="308">
         <f>L30-K30</f>
@@ -30737,7 +30737,7 @@
         <v>10850</v>
       </c>
       <c r="S30" s="368" t="n">
-        <v>11355.972</v>
+        <v>11356.045</v>
       </c>
       <c r="T30" s="308">
         <f>S30-R30</f>
@@ -30981,7 +30981,7 @@
         <v>9100</v>
       </c>
       <c r="L33" s="355" t="n">
-        <v>10613</v>
+        <v>10666.07</v>
       </c>
       <c r="M33" s="317">
         <f>L33-K33</f>
@@ -31005,7 +31005,7 @@
         <v>2050</v>
       </c>
       <c r="S33" s="351" t="n">
-        <v>2668</v>
+        <v>2678.446999999999</v>
       </c>
       <c r="T33" s="317">
         <f>S33-R33</f>
@@ -31685,7 +31685,7 @@
         <v>46340</v>
       </c>
       <c r="L41" s="306" t="n">
-        <v>54652.489</v>
+        <v>54652.012</v>
       </c>
       <c r="M41" s="308">
         <f>L41-K41</f>
@@ -31709,7 +31709,7 @@
         <v>14640</v>
       </c>
       <c r="S41" s="306" t="n">
-        <v>17486.522</v>
+        <v>17486.074</v>
       </c>
       <c r="T41" s="308">
         <f>S41-R41</f>
@@ -32750,7 +32750,7 @@
         <v>73350</v>
       </c>
       <c r="L5" s="306" t="n">
-        <v>86809.298</v>
+        <v>86809.795</v>
       </c>
       <c r="M5" s="308">
         <f>L5-K5</f>
@@ -32774,7 +32774,7 @@
         <v>19540</v>
       </c>
       <c r="S5" s="310" t="n">
-        <v>24673.721</v>
+        <v>24673.819</v>
       </c>
       <c r="T5" s="308">
         <f>S5-R5</f>
@@ -33700,7 +33700,7 @@
         <v>32650</v>
       </c>
       <c r="L16" s="306" t="n">
-        <v>40383.262</v>
+        <v>40383.75900000001</v>
       </c>
       <c r="M16" s="308">
         <f>L16-K16</f>
@@ -33724,7 +33724,7 @@
         <v>8630</v>
       </c>
       <c r="S16" s="306" t="n">
-        <v>10567.872</v>
+        <v>10565.4129</v>
       </c>
       <c r="T16" s="308">
         <f>S16-R16</f>
@@ -34136,7 +34136,7 @@
         <v>47900</v>
       </c>
       <c r="L21" s="357" t="n">
-        <v>42974</v>
+        <v>42973.586</v>
       </c>
       <c r="M21" s="308">
         <f>L21-K21</f>
@@ -34160,7 +34160,7 @@
         <v>7125</v>
       </c>
       <c r="S21" s="357" t="n">
-        <v>6723</v>
+        <v>6723.144</v>
       </c>
       <c r="T21" s="308">
         <f>S21-R21</f>
@@ -35198,7 +35198,7 @@
         <v>28100</v>
       </c>
       <c r="L33" s="355" t="n">
-        <v>22304.8</v>
+        <v>23011.7</v>
       </c>
       <c r="M33" s="317">
         <f>L33-K33</f>
@@ -35222,7 +35222,7 @@
         <v>4320</v>
       </c>
       <c r="S33" s="351" t="n">
-        <v>3097.852</v>
+        <v>3269.552</v>
       </c>
       <c r="T33" s="317">
         <f>S33-R33</f>
@@ -35902,7 +35902,7 @@
         <v>41800</v>
       </c>
       <c r="L41" s="306" t="n">
-        <v>56225</v>
+        <v>56224.308</v>
       </c>
       <c r="M41" s="308">
         <f>L41-K41</f>
@@ -35926,7 +35926,7 @@
         <v>13420</v>
       </c>
       <c r="S41" s="306" t="n">
-        <v>16777</v>
+        <v>16778.798</v>
       </c>
       <c r="T41" s="308">
         <f>S41-R41</f>
@@ -36074,7 +36074,7 @@
         <v>7790</v>
       </c>
       <c r="L43" s="390" t="n">
-        <v>5509.048</v>
+        <v>7893.774</v>
       </c>
       <c r="M43" s="345">
         <f>L43-K43</f>
@@ -36098,7 +36098,7 @@
         <v>4630</v>
       </c>
       <c r="S43" s="390" t="n">
-        <v>3761.495</v>
+        <v>4502.391</v>
       </c>
       <c r="T43" s="345">
         <f>S43-R43</f>
@@ -36152,7 +36152,7 @@
         <v>90</v>
       </c>
       <c r="L44" s="390" t="n">
-        <v>100</v>
+        <v>100.17</v>
       </c>
       <c r="M44" s="345">
         <f>L44-K44</f>
@@ -36176,7 +36176,7 @@
         <v>20</v>
       </c>
       <c r="S44" s="390" t="n">
-        <v>21</v>
+        <v>21.51</v>
       </c>
       <c r="T44" s="345">
         <f>S44-R44</f>

--- a/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
@@ -2685,14 +2685,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
     <col width="2.875" customWidth="1" style="1" min="5" max="5"/>
     <col width="3.125" customWidth="1" style="1" min="6" max="7"/>
     <col width="16" customWidth="1" style="1" min="8" max="8"/>
+    <col width="13" customWidth="1" style="1" min="9" max="9"/>
+    <col width="13" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13" customWidth="1" style="1" min="11" max="11"/>
+    <col width="13" customWidth="1" style="1" min="12" max="12"/>
     <col width="8.5" customWidth="1" style="302" min="13" max="14"/>
+    <col width="13" customWidth="1" style="1" min="16" max="16"/>
+    <col width="13" customWidth="1" style="1" min="17" max="17"/>
+    <col width="13" customWidth="1" style="1" min="18" max="18"/>
+    <col width="13" customWidth="1" style="1" min="19" max="19"/>
     <col width="8.5" customWidth="1" style="302" min="20" max="21"/>
     <col width="60.5" customWidth="1" style="1" min="29" max="29"/>
   </cols>
@@ -2704,7 +2712,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -6902,15 +6909,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
     <col width="2.875" customWidth="1" style="1" min="5" max="5"/>
     <col width="3.125" customWidth="1" style="1" min="6" max="7"/>
     <col width="16" customWidth="1" style="1" min="8" max="8"/>
-    <col width="8.75" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
+    <col width="13" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
+    <col width="13" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13" customWidth="1" style="1" min="11" max="11"/>
+    <col width="13" customWidth="1" style="1" min="12" max="12"/>
     <col width="8.5" customWidth="1" style="302" min="13" max="14"/>
+    <col width="13" customWidth="1" style="1" min="16" max="16"/>
+    <col width="13" customWidth="1" style="1" min="17" max="17"/>
+    <col width="13" customWidth="1" style="1" min="18" max="18"/>
+    <col width="13" customWidth="1" style="1" min="19" max="19"/>
     <col width="8.5" customWidth="1" style="302" min="20" max="21"/>
     <col width="60.5" customWidth="1" style="1" min="29" max="29"/>
   </cols>
@@ -6922,7 +6936,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -11296,17 +11309,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
     <col width="2.875" customWidth="1" style="1" min="5" max="5"/>
     <col width="3.125" customWidth="1" style="1" min="6" max="7"/>
     <col width="16" customWidth="1" style="1" min="8" max="8"/>
-    <col width="9.875" customWidth="1" style="302" min="9" max="9"/>
-    <col width="10" bestFit="1" customWidth="1" style="302" min="10" max="12"/>
+    <col width="14" customWidth="1" style="302" min="9" max="9"/>
+    <col width="14" bestFit="1" customWidth="1" style="302" min="10" max="12"/>
+    <col width="14" customWidth="1" style="1" min="11" max="11"/>
+    <col width="14" customWidth="1" style="1" min="12" max="12"/>
     <col width="8.625" bestFit="1" customWidth="1" style="302" min="13" max="14"/>
-    <col width="8.5" customWidth="1" style="302" min="16" max="21"/>
+    <col width="14" customWidth="1" style="302" min="16" max="21"/>
+    <col width="14" customWidth="1" style="1" min="17" max="17"/>
+    <col width="14" customWidth="1" style="1" min="18" max="18"/>
+    <col width="14" customWidth="1" style="1" min="19" max="19"/>
+    <col width="13" customWidth="1" style="1" min="23" max="23"/>
+    <col width="13" customWidth="1" style="1" min="24" max="24"/>
+    <col width="13" customWidth="1" style="1" min="25" max="25"/>
+    <col width="13" customWidth="1" style="1" min="26" max="26"/>
     <col width="60.5" customWidth="1" style="1" min="29" max="29"/>
   </cols>
   <sheetData>
@@ -11317,7 +11339,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -15703,7 +15724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -15722,7 +15743,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -19920,7 +19940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -19939,7 +19959,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -24137,7 +24156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -24156,7 +24175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -28354,7 +28372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -28373,7 +28391,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -32571,7 +32588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="D1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -32590,7 +32607,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -36788,7 +36804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI50"/>
+  <dimension ref="D1:DI50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" style="1" min="1" max="2"/>
@@ -36809,7 +36825,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="9.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -54435,10 +54450,10 @@
     <mergeCell ref="Z3:Z4"/>
     <mergeCell ref="BH3:BH4"/>
     <mergeCell ref="BN3:BN4"/>
+    <mergeCell ref="BT3:BT4"/>
+    <mergeCell ref="BP3:BP4"/>
+    <mergeCell ref="BI3:BI4"/>
     <mergeCell ref="CQ3:CQ4"/>
-    <mergeCell ref="BT3:BT4"/>
-    <mergeCell ref="BI3:BI4"/>
-    <mergeCell ref="BP3:BP4"/>
     <mergeCell ref="CB3:CB4"/>
     <mergeCell ref="DE3:DE4"/>
     <mergeCell ref="BA3:BA4"/>

--- a/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
@@ -2685,7 +2685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -2712,6 +2712,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -6909,7 +6910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -6936,6 +6937,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -11309,7 +11311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -11339,6 +11341,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -15724,7 +15727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -15743,6 +15746,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -19940,7 +19944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -19959,6 +19963,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -24156,7 +24161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -24175,6 +24180,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -28372,7 +28378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -28391,6 +28397,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -32588,7 +32595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="D1:AC50"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col width="2.375" customWidth="1" style="1" min="4" max="4"/>
@@ -32607,6 +32614,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -36804,7 +36812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D1:DI50"/>
+  <dimension ref="A1:DI50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="18.75"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" style="1" min="1" max="2"/>
@@ -36825,6 +36833,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="9.75" customHeight="1" s="1">
       <c r="D3" s="284" t="n"/>
       <c r="E3" s="285" t="n"/>
@@ -54450,10 +54459,10 @@
     <mergeCell ref="Z3:Z4"/>
     <mergeCell ref="BH3:BH4"/>
     <mergeCell ref="BN3:BN4"/>
+    <mergeCell ref="BI3:BI4"/>
     <mergeCell ref="BT3:BT4"/>
+    <mergeCell ref="CQ3:CQ4"/>
     <mergeCell ref="BP3:BP4"/>
-    <mergeCell ref="BI3:BI4"/>
-    <mergeCell ref="CQ3:CQ4"/>
     <mergeCell ref="CB3:CB4"/>
     <mergeCell ref="DE3:DE4"/>
     <mergeCell ref="BA3:BA4"/>

--- a/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期9月実績.xlsx
@@ -6441,19 +6441,19 @@
         </is>
       </c>
       <c r="I46" s="401">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="402">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -6469,19 +6469,19 @@
         <v/>
       </c>
       <c r="P46" s="406">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="403">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -10834,19 +10834,19 @@
         </is>
       </c>
       <c r="I46" s="401">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="402">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -10862,19 +10862,19 @@
         <v/>
       </c>
       <c r="P46" s="401">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="402">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -15250,19 +15250,19 @@
         </is>
       </c>
       <c r="I46" s="477">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="478">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="479">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="479">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -15278,19 +15278,19 @@
         <v/>
       </c>
       <c r="P46" s="477">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="478">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="479">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="479">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -19475,19 +19475,19 @@
         </is>
       </c>
       <c r="I46" s="401">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="402">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -19503,19 +19503,19 @@
         <v/>
       </c>
       <c r="P46" s="406">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="403">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -23692,19 +23692,19 @@
         </is>
       </c>
       <c r="I46" s="401">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="402">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -23720,19 +23720,19 @@
         <v/>
       </c>
       <c r="P46" s="406">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="403">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -27909,19 +27909,19 @@
         </is>
       </c>
       <c r="I46" s="401">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="402">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -27937,19 +27937,19 @@
         <v/>
       </c>
       <c r="P46" s="406">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="403">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -32126,19 +32126,19 @@
         </is>
       </c>
       <c r="I46" s="401">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="402">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -32154,19 +32154,19 @@
         <v/>
       </c>
       <c r="P46" s="406">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="403">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -36343,19 +36343,19 @@
         </is>
       </c>
       <c r="I46" s="401">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="402">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="404">
@@ -36371,19 +36371,19 @@
         <v/>
       </c>
       <c r="P46" s="406">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="403">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="404">
@@ -52868,19 +52868,19 @@
         </is>
       </c>
       <c r="I46" s="420">
-        <f>I45-I47</f>
+        <f>I45-I47-I48-I49</f>
         <v/>
       </c>
       <c r="J46" s="403">
-        <f>J45-J47</f>
+        <f>J45-J47-J48-J49</f>
         <v/>
       </c>
       <c r="K46" s="403">
-        <f>K45-K47</f>
+        <f>K45-K47-K48-K49</f>
         <v/>
       </c>
       <c r="L46" s="403">
-        <f>L45-L47</f>
+        <f>L45-L47-L48-L49</f>
         <v/>
       </c>
       <c r="M46" s="500">
@@ -52896,19 +52896,19 @@
         <v/>
       </c>
       <c r="P46" s="406">
-        <f>P45-P47</f>
+        <f>P45-P47-P48-P49</f>
         <v/>
       </c>
       <c r="Q46" s="403">
-        <f>Q45-Q47</f>
+        <f>Q45-Q47-Q48-Q49</f>
         <v/>
       </c>
       <c r="R46" s="403">
-        <f>R45-R47</f>
+        <f>R45-R47-R48-R49</f>
         <v/>
       </c>
       <c r="S46" s="403">
-        <f>S45-S47</f>
+        <f>S45-S47-S48-S49</f>
         <v/>
       </c>
       <c r="T46" s="500">
@@ -52924,19 +52924,19 @@
         <v/>
       </c>
       <c r="W46" s="420">
-        <f>W45-W47</f>
+        <f>W45-W47-W48-W49</f>
         <v/>
       </c>
       <c r="X46" s="403">
-        <f>X45-X47</f>
+        <f>X45-X47-X48-X49</f>
         <v/>
       </c>
       <c r="Y46" s="403">
-        <f>Y45-Y47</f>
+        <f>Y45-Y47-Y48-Y49</f>
         <v/>
       </c>
       <c r="Z46" s="403">
-        <f>Z45-Z47</f>
+        <f>Z45-Z47-Z48-Z49</f>
         <v/>
       </c>
       <c r="AA46" s="500">
@@ -52952,19 +52952,19 @@
         <v/>
       </c>
       <c r="AD46" s="406">
-        <f>AD45-AD47</f>
+        <f>AD45-AD47-AD48-AD49</f>
         <v/>
       </c>
       <c r="AE46" s="403">
-        <f>AE45-AE47</f>
+        <f>AE45-AE47-AE48-AE49</f>
         <v/>
       </c>
       <c r="AF46" s="403">
-        <f>AF45-AF47</f>
+        <f>AF45-AF47-AF48-AF49</f>
         <v/>
       </c>
       <c r="AG46" s="403">
-        <f>AG45-AG47</f>
+        <f>AG45-AG47-AG48-AG49</f>
         <v/>
       </c>
       <c r="AH46" s="500">
@@ -52980,19 +52980,19 @@
         <v/>
       </c>
       <c r="AK46" s="420">
-        <f>AK45-AK47</f>
+        <f>AK45-AK47-AK48-AK49</f>
         <v/>
       </c>
       <c r="AL46" s="403">
-        <f>AL45-AL47</f>
+        <f>AL45-AL47-AL48-AL49</f>
         <v/>
       </c>
       <c r="AM46" s="403">
-        <f>AM45-AM47</f>
+        <f>AM45-AM47-AM48-AM49</f>
         <v/>
       </c>
       <c r="AN46" s="403">
-        <f>AN45-AN47</f>
+        <f>AN45-AN47-AN48-AN49</f>
         <v/>
       </c>
       <c r="AO46" s="500">
@@ -53008,19 +53008,19 @@
         <v/>
       </c>
       <c r="AR46" s="406">
-        <f>AR45-AR47</f>
+        <f>AR45-AR47-AR48-AR49</f>
         <v/>
       </c>
       <c r="AS46" s="403">
-        <f>AS45-AS47</f>
+        <f>AS45-AS47-AS48-AS49</f>
         <v/>
       </c>
       <c r="AT46" s="403">
-        <f>AT45-AT47</f>
+        <f>AT45-AT47-AT48-AT49</f>
         <v/>
       </c>
       <c r="AU46" s="403">
-        <f>AU45-AU47</f>
+        <f>AU45-AU47-AU48-AU49</f>
         <v/>
       </c>
       <c r="AV46" s="500">
@@ -53036,19 +53036,19 @@
         <v/>
       </c>
       <c r="AY46" s="420">
-        <f>AY45-AY47</f>
+        <f>AY45-AY47-AY48-AY49</f>
         <v/>
       </c>
       <c r="AZ46" s="403">
-        <f>AZ45-AZ47</f>
+        <f>AZ45-AZ47-AZ48-AZ49</f>
         <v/>
       </c>
       <c r="BA46" s="403">
-        <f>BA45-BA47</f>
+        <f>BA45-BA47-BA48-BA49</f>
         <v/>
       </c>
       <c r="BB46" s="403">
-        <f>BB45-BB47</f>
+        <f>BB45-BB47-BB48-BB49</f>
         <v/>
       </c>
       <c r="BC46" s="500">
@@ -53064,19 +53064,19 @@
         <v/>
       </c>
       <c r="BF46" s="406">
-        <f>BF45-BF47</f>
+        <f>BF45-BF47-BF48-BF49</f>
         <v/>
       </c>
       <c r="BG46" s="403">
-        <f>BG45-BG47</f>
+        <f>BG45-BG47-BG48-BG49</f>
         <v/>
       </c>
       <c r="BH46" s="403">
-        <f>BH45-BH47</f>
+        <f>BH45-BH47-BH48-BH49</f>
         <v/>
       </c>
       <c r="BI46" s="403">
-        <f>BI45-BI47</f>
+        <f>BI45-BI47-BI48-BI49</f>
         <v/>
       </c>
       <c r="BJ46" s="500">
@@ -53092,19 +53092,19 @@
         <v/>
       </c>
       <c r="BM46" s="420">
-        <f>BM45-BM47</f>
+        <f>BM45-BM47-BM48-BM49</f>
         <v/>
       </c>
       <c r="BN46" s="403">
-        <f>BN45-BN47</f>
+        <f>BN45-BN47-BN48-BN49</f>
         <v/>
       </c>
       <c r="BO46" s="403">
-        <f>BO45-BO47</f>
+        <f>BO45-BO47-BO48-BO49</f>
         <v/>
       </c>
       <c r="BP46" s="403">
-        <f>BP45-BP47</f>
+        <f>BP45-BP47-BP48-BP49</f>
         <v/>
       </c>
       <c r="BQ46" s="500">
@@ -53120,19 +53120,19 @@
         <v/>
       </c>
       <c r="BT46" s="406">
-        <f>BT45-BT47</f>
+        <f>BT45-BT47-BT48-BT49</f>
         <v/>
       </c>
       <c r="BU46" s="403">
-        <f>BU45-BU47</f>
+        <f>BU45-BU47-BU48-BU49</f>
         <v/>
       </c>
       <c r="BV46" s="403">
-        <f>BV45-BV47</f>
+        <f>BV45-BV47-BV48-BV49</f>
         <v/>
       </c>
       <c r="BW46" s="403">
-        <f>BW45-BW47</f>
+        <f>BW45-BW47-BW48-BW49</f>
         <v/>
       </c>
       <c r="BX46" s="500">
@@ -53148,19 +53148,19 @@
         <v/>
       </c>
       <c r="CA46" s="420">
-        <f>CA45-CA47</f>
+        <f>CA45-CA47-CA48-CA49</f>
         <v/>
       </c>
       <c r="CB46" s="403">
-        <f>CB45-CB47</f>
+        <f>CB45-CB47-CB48-CB49</f>
         <v/>
       </c>
       <c r="CC46" s="403">
-        <f>CC45-CC47</f>
+        <f>CC45-CC47-CC48-CC49</f>
         <v/>
       </c>
       <c r="CD46" s="403">
-        <f>CD45-CD47</f>
+        <f>CD45-CD47-CD48-CD49</f>
         <v/>
       </c>
       <c r="CE46" s="500">
@@ -53176,19 +53176,19 @@
         <v/>
       </c>
       <c r="CH46" s="406">
-        <f>CH45-CH47</f>
+        <f>CH45-CH47-CH48-CH49</f>
         <v/>
       </c>
       <c r="CI46" s="403">
-        <f>CI45-CI47</f>
+        <f>CI45-CI47-CI48-CI49</f>
         <v/>
       </c>
       <c r="CJ46" s="403">
-        <f>CJ45-CJ47</f>
+        <f>CJ45-CJ47-CJ48-CJ49</f>
         <v/>
       </c>
       <c r="CK46" s="403">
-        <f>CK45-CK47</f>
+        <f>CK45-CK47-CK48-CK49</f>
         <v/>
       </c>
       <c r="CL46" s="500">
@@ -53204,19 +53204,19 @@
         <v/>
       </c>
       <c r="CO46" s="401">
-        <f>CO45-CO47</f>
+        <f>CO45-CO47-CO48-CO49</f>
         <v/>
       </c>
       <c r="CP46" s="402">
-        <f>CP45-CP47</f>
+        <f>CP45-CP47-CP48-CP49</f>
         <v/>
       </c>
       <c r="CQ46" s="403">
-        <f>CQ45-CQ47</f>
+        <f>CQ45-CQ47-CQ48-CQ49</f>
         <v/>
       </c>
       <c r="CR46" s="403">
-        <f>CR45-CR47</f>
+        <f>CR45-CR47-CR48-CR49</f>
         <v/>
       </c>
       <c r="CS46" s="500">
@@ -53232,19 +53232,19 @@
         <v/>
       </c>
       <c r="CV46" s="406">
-        <f>CV45-CV47</f>
+        <f>CV45-CV47-CV48-CV49</f>
         <v/>
       </c>
       <c r="CW46" s="403">
-        <f>CW45-CW47</f>
+        <f>CW45-CW47-CW48-CW49</f>
         <v/>
       </c>
       <c r="CX46" s="403">
-        <f>CX45-CX47</f>
+        <f>CX45-CX47-CX48-CX49</f>
         <v/>
       </c>
       <c r="CY46" s="403">
-        <f>CY45-CY47</f>
+        <f>CY45-CY47-CY48-CY49</f>
         <v/>
       </c>
       <c r="CZ46" s="500">
@@ -54459,10 +54459,10 @@
     <mergeCell ref="Z3:Z4"/>
     <mergeCell ref="BH3:BH4"/>
     <mergeCell ref="BN3:BN4"/>
+    <mergeCell ref="BT3:BT4"/>
+    <mergeCell ref="BP3:BP4"/>
     <mergeCell ref="BI3:BI4"/>
-    <mergeCell ref="BT3:BT4"/>
     <mergeCell ref="CQ3:CQ4"/>
-    <mergeCell ref="BP3:BP4"/>
     <mergeCell ref="CB3:CB4"/>
     <mergeCell ref="DE3:DE4"/>
     <mergeCell ref="BA3:BA4"/>
